--- a/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
+++ b/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 01:12:07</t>
+          <t>2026-07-04 01:24:22</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,34 +558,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Grantee 'Acme Minerals LLC' (2019-03-20) != next grantor 'John Q. Sample' (2019-03-20)</t>
+          <t>Grantee 'Acme Minerals LLC' (2019-03-20) != next grantor 'Foo' (2099-12-31)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>01_warranty_deed.txt; 01_warranty_deed_COPY.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>chain-gap</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SEC 12-T7N-R63W</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Grantee 'Acme Minerals LLC' (2019-03-20) != next grantor 'Foo' (2099-12-31)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>01_warranty_deed_COPY.txt; 07_bad_date.txt</t>
+          <t>01_warranty_deed.txt; 07_bad_date.txt</t>
         </is>
       </c>
     </row>

--- a/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
+++ b/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 01:24:22</t>
+          <t>2026-07-04 01:29:06</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>04_ownership_note.txt; 04_ownership_note.txt</t>
+          <t>04_ownership_note.txt</t>
         </is>
       </c>
     </row>

--- a/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
+++ b/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 01:29:06</t>
+          <t>2026-07-04 01:32:17</t>
         </is>
       </c>
     </row>

--- a/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
+++ b/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 01:32:17</t>
+          <t>2026-07-04 01:39:11</t>
         </is>
       </c>
     </row>

--- a/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
+++ b/examples/sample_output_synthetic/conflicts_and_gaps.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 01:39:11</t>
+          <t>2026-07-04 01:49:11</t>
         </is>
       </c>
     </row>
